--- a/JsonConverter/ExcelFiles/CompanionData.xlsx
+++ b/JsonConverter/ExcelFiles/CompanionData.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\ProjectC\JsonConverter\ExelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\ProjectC\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -21,118 +21,118 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <x:si>
+    <x:t>등급</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김환</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이아진</x:t>
+  </x:si>
+  <x:si>
+    <x:t>장준성</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김경민</x:t>
+  </x:si>
+  <x:si>
+    <x:t>김희주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Companion_001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Companion_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Companion_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Companion_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Companion_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 방어력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SkillId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본 공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기본HP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>float</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성장 방어력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성장 HP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성장 공격력</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseDef</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BaseHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrowthDef</x:t>
+  </x:si>
+  <x:si>
+    <x:t>보유 스킬 id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Skill_003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Skill_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Skill_004</x:t>
+  </x:si>
+  <x:si>
     <x:t>GrowthHp</x:t>
   </x:si>
   <x:si>
     <x:t>GradeStar</x:t>
   </x:si>
   <x:si>
-    <x:t>보유 스킬 id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>엘리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피어스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseDef</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Skill_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Skill_004</x:t>
-  </x:si>
-  <x:si>
     <x:t>Skill_005</x:t>
   </x:si>
   <x:si>
-    <x:t>Skill_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>오스왈드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Companion_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>등급</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Companion_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Companion_004</x:t>
+    <x:t>캐릭터 고유id</x:t>
   </x:si>
   <x:si>
     <x:t>GrowthAtk</x:t>
   </x:si>
   <x:si>
-    <x:t>Companion_002</x:t>
-  </x:si>
-  <x:si>
     <x:t>Skill_001</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 공격력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>float</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본HP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기본 방어력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성장 방어력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성장 HP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성장 공격력</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrowthDef</x:t>
-  </x:si>
-  <x:si>
-    <x:t>앤더슨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>다니엘</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Companion_003</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SkillId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BaseAtk</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1662,34 +1662,34 @@
   <x:sheetData>
     <x:row r="1" spans="1:21" s="29" customFormat="1">
       <x:c r="A1" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B1" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D1" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E1" s="5" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F1" s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G1" s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="H1" s="5" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="C1" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D1" s="5" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E1" s="5" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F1" s="6" t="s">
+      <x:c r="I1" s="7" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J1" s="7" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="G1" s="6" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="H1" s="5" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I1" s="7" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="J1" s="7" t="s">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="K1" s="7"/>
       <x:c r="L1" s="7"/>
@@ -1705,34 +1705,34 @@
     </x:row>
     <x:row r="2" spans="1:21" s="29" customFormat="1">
       <x:c r="A2" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D2" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E2" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F2" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G2" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="I2" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="J2" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K2" s="7"/>
       <x:c r="L2" s="7"/>
@@ -1748,34 +1748,34 @@
     </x:row>
     <x:row r="3" spans="1:21" s="29" customFormat="1">
       <x:c r="A3" s="9" t="s">
-        <x:v>15</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="9" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D3" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E3" s="10" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H3" s="10" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C3" s="9" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="10" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E3" s="10" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="F3" s="11" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G3" s="11" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H3" s="10" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I3" s="12" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="J3" s="12" t="s">
-        <x:v>36</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K3" s="12"/>
       <x:c r="L3" s="12"/>
@@ -1791,10 +1791,10 @@
     </x:row>
     <x:row r="4" spans="1:21" s="30" customFormat="1">
       <x:c r="A4" s="20" t="s">
-        <x:v>12</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="20" t="s">
-        <x:v>34</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="20">
         <x:v>1</x:v>
@@ -1818,7 +1818,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="J4" s="23" t="s">
-        <x:v>20</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K4" s="23"/>
       <x:c r="L4" s="23"/>
@@ -1834,10 +1834,10 @@
     </x:row>
     <x:row r="5" spans="1:21" s="30" customFormat="1">
       <x:c r="A5" s="20" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="26" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C5" s="26">
         <x:v>1</x:v>
@@ -1861,7 +1861,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J5" s="23" t="s">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="K5" s="23"/>
       <x:c r="L5" s="23"/>
@@ -1877,10 +1877,10 @@
     </x:row>
     <x:row r="6" spans="1:21" s="30" customFormat="1">
       <x:c r="A6" s="20" t="s">
-        <x:v>35</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="26" t="s">
-        <x:v>33</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C6" s="26">
         <x:v>2</x:v>
@@ -1904,7 +1904,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J6" s="27" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K6" s="27"/>
       <x:c r="L6" s="27"/>
@@ -1920,10 +1920,10 @@
     </x:row>
     <x:row r="7" spans="1:21" s="30" customFormat="1">
       <x:c r="A7" s="20" t="s">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="26" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C7" s="26">
         <x:v>3</x:v>
@@ -1947,7 +1947,7 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="J7" s="27" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K7" s="27"/>
       <x:c r="L7" s="27"/>
@@ -1963,10 +1963,10 @@
     </x:row>
     <x:row r="8" spans="1:21" s="30" customFormat="1">
       <x:c r="A8" s="20" t="s">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B8" s="20" t="s">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C8" s="20">
         <x:v>3</x:v>
@@ -1990,7 +1990,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="J8" s="27" t="s">
-        <x:v>9</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="K8" s="27"/>
       <x:c r="L8" s="27"/>

--- a/JsonConverter/ExcelFiles/CompanionData.xlsx
+++ b/JsonConverter/ExcelFiles/CompanionData.xlsx
@@ -169,10 +169,10 @@
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -187,40 +187,40 @@
     <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -704,8 +704,8 @@
       <c r="B7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="11">
-        <v>3.0</v>
+      <c r="C7" s="12">
+        <v>4.0</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>21</v>

--- a/JsonConverter/ExcelFiles/CompanionData.xlsx
+++ b/JsonConverter/ExcelFiles/CompanionData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="65">
   <si>
     <t>동료 고유 ID</t>
   </si>
@@ -46,13 +46,22 @@
     <t>일반 스킬 가속</t>
   </si>
   <si>
-    <t>특수 스킬 가속</t>
+    <t>고유 스킬 가속</t>
   </si>
   <si>
     <t>기본 공격 스킬 ID</t>
   </si>
   <si>
-    <t>액티브 스킬 ID</t>
+    <t>고유 스킬 ID</t>
+  </si>
+  <si>
+    <t>동료 목록 슬롯 스프라이트 Addressable Key</t>
+  </si>
+  <si>
+    <t>전투 스킬 버튼 스프라이트 Addressable Key</t>
+  </si>
+  <si>
+    <t>애니메이션 세트 Addressable Key</t>
   </si>
   <si>
     <t>string</t>
@@ -97,13 +106,22 @@
     <t>BasicAttackHaste</t>
   </si>
   <si>
-    <t>ActiveSkillHaste</t>
+    <t>SignatureSkillHaste</t>
   </si>
   <si>
     <t>BasicAttackSkillId</t>
   </si>
   <si>
-    <t>ActiveSkillId</t>
+    <t>SignatureSkillId</t>
+  </si>
+  <si>
+    <t>SlotSpriteAddressableKey</t>
+  </si>
+  <si>
+    <t>PortraitSpriteAddressableKey</t>
+  </si>
+  <si>
+    <t>AnimationSetKey</t>
   </si>
   <si>
     <t>companion_001</t>
@@ -118,6 +136,15 @@
     <t>skill_companion_001_active</t>
   </si>
   <si>
+    <t>Sprite/companion_001_slot</t>
+  </si>
+  <si>
+    <t>Sprite/companion_001_portrait</t>
+  </si>
+  <si>
+    <t>Anim/companion_001</t>
+  </si>
+  <si>
     <t>companion_002</t>
   </si>
   <si>
@@ -130,6 +157,15 @@
     <t>skill_companion_002_active</t>
   </si>
   <si>
+    <t>Sprite/companion_002_slot</t>
+  </si>
+  <si>
+    <t>Sprite/companion_002_portrait</t>
+  </si>
+  <si>
+    <t>Anim/companion_002</t>
+  </si>
+  <si>
     <t>companion_003</t>
   </si>
   <si>
@@ -142,6 +178,15 @@
     <t>skill_companion_003_active</t>
   </si>
   <si>
+    <t>Sprite/companion_003_slot</t>
+  </si>
+  <si>
+    <t>Sprite/companion_003_portrait</t>
+  </si>
+  <si>
+    <t>Anim/companion_003</t>
+  </si>
+  <si>
     <t>companion_004</t>
   </si>
   <si>
@@ -152,13 +197,22 @@
   </si>
   <si>
     <t>skill_companion_004_active</t>
+  </si>
+  <si>
+    <t>Sprite/companion_004_slot</t>
+  </si>
+  <si>
+    <t>Sprite/companion_004_portrait</t>
+  </si>
+  <si>
+    <t>Anim/companion_004</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -174,6 +228,11 @@
     <font>
       <sz val="11.0"/>
       <color rgb="FF1F1F1F"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -217,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -229,6 +288,9 @@
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,7 +520,7 @@
     <col customWidth="1" min="9" max="9" width="22.0"/>
     <col customWidth="1" min="10" max="12" width="18.0"/>
     <col customWidth="1" min="13" max="14" width="30.0"/>
-    <col customWidth="1" min="15" max="26" width="8.63"/>
+    <col customWidth="1" min="15" max="17" width="8.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1">
@@ -504,101 +566,128 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2" ht="33.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="3" ht="33.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" ht="24.0" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C4" s="3">
         <v>1.0</v>
@@ -631,18 +720,27 @@
         <v>0.0</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="5" ht="24.0" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C5" s="3">
         <v>2.0</v>
@@ -675,18 +773,27 @@
         <v>0.0</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="6" ht="24.0" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C6" s="3">
         <v>3.0</v>
@@ -719,18 +826,27 @@
         <v>0.0</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="7" ht="24.0" customHeight="1">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C7" s="3">
         <v>4.0</v>
@@ -763,10 +879,19 @@
         <v>0.0</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>46</v>
+        <v>61</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/CompanionData.xlsx
+++ b/JsonConverter/ExcelFiles/CompanionData.xlsx
@@ -127,7 +127,7 @@
     <t>companion_001</t>
   </si>
   <si>
-    <t>임시1</t>
+    <t>방패 용사 레온</t>
   </si>
   <si>
     <t>skill_companion_001_basic</t>
@@ -148,7 +148,7 @@
     <t>companion_002</t>
   </si>
   <si>
-    <t>임시2</t>
+    <t>명사수 리아</t>
   </si>
   <si>
     <t>skill_companion_002_basic</t>
@@ -169,7 +169,7 @@
     <t>companion_003</t>
   </si>
   <si>
-    <t>임시3</t>
+    <t>홍염의 세라</t>
   </si>
   <si>
     <t>skill_companion_003_basic</t>
@@ -190,7 +190,7 @@
     <t>companion_004</t>
   </si>
   <si>
-    <t>임시4</t>
+    <t>쌍월의 카인</t>
   </si>
   <si>
     <t>skill_companion_004_basic</t>
@@ -212,6 +212,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.###"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <sz val="11.0"/>
@@ -276,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -284,13 +287,16 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -520,10 +526,12 @@
     <col customWidth="1" min="9" max="9" width="22.0"/>
     <col customWidth="1" min="10" max="12" width="18.0"/>
     <col customWidth="1" min="13" max="14" width="30.0"/>
-    <col customWidth="1" min="15" max="17" width="8.63"/>
+    <col customWidth="1" min="15" max="15" width="20.5"/>
+    <col customWidth="1" min="16" max="16" width="22.25"/>
+    <col customWidth="1" min="17" max="17" width="40.75"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33.75" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -693,31 +701,31 @@
         <v>1.0</v>
       </c>
       <c r="D4" s="3">
-        <v>520.0</v>
+        <v>1300.0</v>
       </c>
       <c r="E4" s="3">
-        <v>40.0</v>
+        <v>100.0</v>
       </c>
       <c r="F4" s="3">
-        <v>48.0</v>
+        <v>100.0</v>
       </c>
       <c r="G4" s="3">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="H4" s="3">
-        <v>23.0</v>
+        <v>152.0</v>
       </c>
       <c r="I4" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="J4" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="J4" s="4">
         <v>0.1</v>
       </c>
       <c r="K4" s="3">
         <v>0.0</v>
       </c>
       <c r="L4" s="3">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>39</v>
@@ -725,13 +733,13 @@
       <c r="N4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="5" t="s">
         <v>43</v>
       </c>
     </row>
@@ -746,31 +754,31 @@
         <v>2.0</v>
       </c>
       <c r="D5" s="3">
-        <v>510.0</v>
+        <v>970.0</v>
       </c>
       <c r="E5" s="3">
-        <v>46.0</v>
+        <v>70.0</v>
       </c>
       <c r="F5" s="3">
-        <v>50.0</v>
+        <v>205.0</v>
       </c>
       <c r="G5" s="3">
-        <v>4.6</v>
+        <v>15.0</v>
       </c>
       <c r="H5" s="3">
-        <v>22.0</v>
+        <v>77.0</v>
       </c>
       <c r="I5" s="3">
-        <v>2.1</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0.1</v>
+        <v>7.0</v>
+      </c>
+      <c r="J5" s="4">
+        <v>0.25</v>
       </c>
       <c r="K5" s="3">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="L5" s="3">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>46</v>
@@ -778,13 +786,13 @@
       <c r="N5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="5" t="s">
         <v>50</v>
       </c>
     </row>
@@ -799,31 +807,31 @@
         <v>3.0</v>
       </c>
       <c r="D6" s="3">
-        <v>530.0</v>
+        <v>1030.0</v>
       </c>
       <c r="E6" s="3">
-        <v>52.0</v>
+        <v>80.0</v>
       </c>
       <c r="F6" s="3">
-        <v>49.0</v>
+        <v>239.0</v>
       </c>
       <c r="G6" s="3">
-        <v>5.2</v>
+        <v>24.0</v>
       </c>
       <c r="H6" s="3">
-        <v>24.0</v>
+        <v>81.0</v>
       </c>
       <c r="I6" s="3">
-        <v>2.4</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0.1</v>
+        <v>6.0</v>
+      </c>
+      <c r="J6" s="4">
+        <v>0.2</v>
       </c>
       <c r="K6" s="3">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="L6" s="3">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>53</v>
@@ -831,13 +839,13 @@
       <c r="N6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="P6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="Q6" s="4" t="s">
+      <c r="Q6" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -852,31 +860,31 @@
         <v>4.0</v>
       </c>
       <c r="D7" s="3">
-        <v>520.0</v>
+        <v>930.0</v>
       </c>
       <c r="E7" s="3">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="F7" s="3">
-        <v>52.0</v>
+        <v>200.0</v>
       </c>
       <c r="G7" s="3">
-        <v>6.0</v>
+        <v>20.0</v>
       </c>
       <c r="H7" s="3">
-        <v>23.0</v>
+        <v>72.0</v>
       </c>
       <c r="I7" s="3">
-        <v>2.8</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0.1</v>
+        <v>7.0</v>
+      </c>
+      <c r="J7" s="4">
+        <v>0.25</v>
       </c>
       <c r="K7" s="3">
-        <v>0.0</v>
+        <v>15.0</v>
       </c>
       <c r="L7" s="3">
-        <v>0.0</v>
+        <v>10.0</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>60</v>
@@ -884,13 +892,13 @@
       <c r="N7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="P7" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="Q7" s="4" t="s">
+      <c r="Q7" s="5" t="s">
         <v>64</v>
       </c>
     </row>
